--- a/public/downloads/PasumarthiFacetDependence2023.xlsx
+++ b/public/downloads/PasumarthiFacetDependence2023.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="MATLANTISv8" sheetId="4" r:id="rId4"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="MATLANTISv8" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="53">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -49,10 +51,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
-  </si>
-  <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_total (ms)</t>
+  </si>
+  <si>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -113,6 +115,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CO</t>
@@ -640,10 +663,10 @@
         <v>400</v>
       </c>
       <c r="N3" s="5">
-        <v>2457.594125747681</v>
+        <v>2457594.125747681</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03226713573010452</v>
+        <v>32.26713573010452</v>
       </c>
       <c r="P3" s="5">
         <v>76164</v>
@@ -690,10 +713,10 @@
         <v>1275</v>
       </c>
       <c r="N4" s="5">
-        <v>17691.29787039757</v>
+        <v>17691297.87039757</v>
       </c>
       <c r="O4" s="4">
-        <v>0.08359383591671267</v>
+        <v>83.59383591671266</v>
       </c>
       <c r="P4" s="5">
         <v>211634</v>
@@ -721,6 +744,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.75</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.25</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.25</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2246851745043986</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1095778606829929</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1277538475919344</v>
+      </c>
+      <c r="K3" s="4">
+        <v>77.1237244897959</v>
+      </c>
+      <c r="L3" s="4">
+        <v>80.60718680089558</v>
+      </c>
+      <c r="M3" s="5">
+        <v>400</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2457594.125747681</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.26713573010452</v>
+      </c>
+      <c r="P3" s="5">
+        <v>76164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>87.21568627450981</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.784313725490196</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.058823529411765</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.725490196078431</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1889538812737588</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.09345439539898084</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.09912643080956657</v>
+      </c>
+      <c r="K4" s="4">
+        <v>82.85684940642921</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.66103434662473</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1275</v>
+      </c>
+      <c r="N4" s="5">
+        <v>17691297.87039757</v>
+      </c>
+      <c r="O4" s="4">
+        <v>83.59383591671266</v>
+      </c>
+      <c r="P4" s="5">
+        <v>211634</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -833,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -877,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -902,9 +1132,192 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>332</v>
+      </c>
+      <c r="C3" s="5">
+        <v>55</v>
+      </c>
+      <c r="D3" s="5">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1112</v>
+      </c>
+      <c r="C4" s="5">
+        <v>102</v>
+      </c>
+      <c r="D4" s="5">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5">
+        <v>39</v>
+      </c>
+      <c r="F4" s="5">
+        <v>22</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>39</v>
+      </c>
+      <c r="I4" s="5">
+        <v>39</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>11</v>
+      </c>
+      <c r="L4" s="5">
+        <v>11</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -915,9 +1328,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -951,8 +1370,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -974,10 +1401,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4">
         <v>0.8485257318287041</v>
@@ -1015,10 +1460,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.8485257318287041</v>
+      </c>
+      <c r="O3" s="5">
+        <v>45</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1323562327661138</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1323562327661138</v>
+      </c>
+      <c r="R3" s="5">
+        <v>45</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4">
         <v>0.4577236848349871</v>
@@ -1056,10 +1519,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4577236848349871</v>
+      </c>
+      <c r="O4" s="5">
+        <v>44</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09383914091960066</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09383914091960066</v>
+      </c>
+      <c r="R4" s="5">
+        <v>44</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4">
         <v>2.040829117108575</v>
@@ -1097,10 +1578,28 @@
       <c r="M5" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-2.008261740876575</v>
+      </c>
+      <c r="O5" s="5">
+        <v>30</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1185777885646744</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09645181705706314</v>
+      </c>
+      <c r="R5" s="5">
+        <v>30</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4">
         <v>2.258260494388444</v>
@@ -1138,10 +1637,28 @@
       <c r="M6" s="5">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-2.19932357874859</v>
+      </c>
+      <c r="O6" s="5">
+        <v>22</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1465948554880125</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1230605664432832</v>
+      </c>
+      <c r="R6" s="5">
+        <v>22</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B7" s="4">
         <v>2.43486569506272</v>
@@ -1179,10 +1696,28 @@
       <c r="M7" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-1.855875738802535</v>
+      </c>
+      <c r="O7" s="5">
+        <v>21</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.648937938302367</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1132491137825804</v>
+      </c>
+      <c r="R7" s="5">
+        <v>21</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4">
         <v>1.362901273534135</v>
@@ -1220,10 +1755,28 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-1.356491776914599</v>
+      </c>
+      <c r="O8" s="5">
+        <v>31</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1023773606339091</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.09906360156322373</v>
+      </c>
+      <c r="R8" s="5">
+        <v>31</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4">
         <v>1.362259446616196</v>
@@ -1261,10 +1814,28 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-1.250883509961726</v>
+      </c>
+      <c r="O9" s="5">
+        <v>23</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.2083668696633512</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1222929155329372</v>
+      </c>
+      <c r="R9" s="5">
+        <v>23</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B10" s="4">
         <v>0.1599472089247088</v>
@@ -1302,10 +1873,28 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.06385642543871654</v>
+      </c>
+      <c r="O10" s="5">
+        <v>25</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1419019075383428</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1022713380757487</v>
+      </c>
+      <c r="R10" s="5">
+        <v>25</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4">
         <v>1.47584030872531</v>
@@ -1343,10 +1932,28 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-1.261090187271394</v>
+      </c>
+      <c r="O11" s="5">
+        <v>18</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.3313264814326249</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1619116110815401</v>
+      </c>
+      <c r="R11" s="5">
+        <v>18</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B12" s="4">
         <v>2.144222546812089</v>
@@ -1384,10 +1991,28 @@
       <c r="M12" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-2.13064501501535</v>
+      </c>
+      <c r="O12" s="5">
+        <v>23</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.1095194438591842</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.1009537727649982</v>
+      </c>
+      <c r="R12" s="5">
+        <v>23</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B13" s="4">
         <v>2.033004752583541</v>
@@ -1425,10 +2050,28 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+      <c r="N13" s="4">
+        <v>-1.529201592586712</v>
+      </c>
+      <c r="O13" s="5">
+        <v>12</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.6806483764339645</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1308584962292419</v>
+      </c>
+      <c r="R13" s="5">
+        <v>12</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4">
         <v>2.080518557382311</v>
@@ -1466,17 +2109,33 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>-1.709509118863934</v>
+      </c>
+      <c r="O14" s="5">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.4170793937137205</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.07678325865890656</v>
+      </c>
+      <c r="R14" s="5">
+        <v>12</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B15" s="4">
         <v>2.291868603765124</v>
       </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
+      <c r="C15" s="4"/>
       <c r="D15" s="4">
         <v>2.18882647806322</v>
       </c>
@@ -1507,10 +2166,28 @@
       <c r="M15" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4">
+        <v>-2.247424341459312</v>
+      </c>
+      <c r="O15" s="5">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.1118748072911633</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.08947386380532407</v>
+      </c>
+      <c r="R15" s="5">
+        <v>12</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4">
         <v>1.952459995274936</v>
@@ -1548,9 +2225,27 @@
       <c r="M16" s="5">
         <v>3</v>
       </c>
+      <c r="N16" s="4">
+        <v>-1.934894883694402</v>
+      </c>
+      <c r="O16" s="5">
+        <v>14</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.08913533517535101</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.0766823824230173</v>
+      </c>
+      <c r="R16" s="5">
+        <v>14</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1561,14 +2256,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1579,9 +2275,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
@@ -1615,8 +2317,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1638,10 +2348,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4">
         <v>0.2338029986133964</v>
@@ -1679,10 +2407,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2072148357632236</v>
+      </c>
+      <c r="O3" s="5">
+        <v>132</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1039704999515591</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08207217571359156</v>
+      </c>
+      <c r="R3" s="5">
+        <v>132</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4">
         <v>0.2077795392892506</v>
@@ -1720,10 +2466,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1849463444931472</v>
+      </c>
+      <c r="O4" s="5">
+        <v>119</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1217816021199155</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1135202785679999</v>
+      </c>
+      <c r="R4" s="5">
+        <v>119</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4">
         <v>0.7682582513851912</v>
@@ -1761,10 +2525,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.7421998810099455</v>
+      </c>
+      <c r="O5" s="5">
+        <v>107</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09942249576447777</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07884929364263252</v>
+      </c>
+      <c r="R5" s="5">
+        <v>107</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4">
         <v>0.6034519698297645</v>
@@ -1802,10 +2584,28 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.5945000713920967</v>
+      </c>
+      <c r="O6" s="5">
+        <v>102</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.08917423772709016</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.08494130042409426</v>
+      </c>
+      <c r="R6" s="5">
+        <v>102</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B7" s="4">
         <v>1.145942552330613</v>
@@ -1843,10 +2643,28 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.7221856090380683</v>
+      </c>
+      <c r="O7" s="5">
+        <v>67</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.4980368309279123</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1020780914056478</v>
+      </c>
+      <c r="R7" s="5">
+        <v>67</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4">
         <v>0.2941774628860007</v>
@@ -1884,10 +2702,28 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.2935755266860084</v>
+      </c>
+      <c r="O8" s="5">
+        <v>99</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.06595677095983789</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.0660149846059047</v>
+      </c>
+      <c r="R8" s="5">
+        <v>99</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4">
         <v>0.5802763429559259</v>
@@ -1925,10 +2761,28 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.395232682680719</v>
+      </c>
+      <c r="O9" s="5">
+        <v>82</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.2636176115108348</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.09486367283325792</v>
+      </c>
+      <c r="R9" s="5">
+        <v>82</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B10" s="4">
         <v>0.1801755381255778</v>
@@ -1966,10 +2820,28 @@
       <c r="M10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>-0.06577525609057178</v>
+      </c>
+      <c r="O10" s="5">
+        <v>79</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1654987478315165</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1022389729834264</v>
+      </c>
+      <c r="R10" s="5">
+        <v>79</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B11" s="4">
         <v>0.4321231714747648</v>
@@ -2007,10 +2879,28 @@
       <c r="M11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>-0.4277782645557701</v>
+      </c>
+      <c r="O11" s="5">
+        <v>83</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.1142954285798121</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.1125999318213191</v>
+      </c>
+      <c r="R11" s="5">
+        <v>83</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B12" s="4">
         <v>0.7559986945664507</v>
@@ -2048,10 +2938,28 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.7136178329554733</v>
+      </c>
+      <c r="O12" s="5">
+        <v>63</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.1507640077299417</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.1238664527073877</v>
+      </c>
+      <c r="R12" s="5">
+        <v>63</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B13" s="4">
         <v>0.7872806478330248</v>
@@ -2089,10 +2997,28 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="25" customHeight="1">
+      <c r="N13" s="4">
+        <v>-0.4384732707200284</v>
+      </c>
+      <c r="O13" s="5">
+        <v>58</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.4426566280913722</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1052092762803198</v>
+      </c>
+      <c r="R13" s="5">
+        <v>58</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4">
         <v>0.7109756367506244</v>
@@ -2130,10 +3056,28 @@
       <c r="M14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="25" customHeight="1">
+      <c r="N14" s="4">
+        <v>-0.5305350749042023</v>
+      </c>
+      <c r="O14" s="5">
+        <v>50</v>
+      </c>
+      <c r="P14" s="4">
+        <v>0.2536585029425361</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0.08840984691756087</v>
+      </c>
+      <c r="R14" s="5">
+        <v>50</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B15" s="4">
         <v>0.8760508020062204</v>
@@ -2171,10 +3115,28 @@
       <c r="M15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="25" customHeight="1">
+      <c r="N15" s="4">
+        <v>-0.5907477696629828</v>
+      </c>
+      <c r="O15" s="5">
+        <v>30</v>
+      </c>
+      <c r="P15" s="4">
+        <v>0.3711836407698618</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0.06710083540820974</v>
+      </c>
+      <c r="R15" s="5">
+        <v>30</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4">
         <v>0.6901173326193689</v>
@@ -2212,9 +3174,27 @@
       <c r="M16" s="5">
         <v>0</v>
       </c>
+      <c r="N16" s="4">
+        <v>-0.6772366297027517</v>
+      </c>
+      <c r="O16" s="5">
+        <v>41</v>
+      </c>
+      <c r="P16" s="4">
+        <v>0.09572973418551789</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>0.08689044742835923</v>
+      </c>
+      <c r="R16" s="5">
+        <v>41</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2225,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/PasumarthiFacetDependence2023.xlsx
+++ b/public/downloads/PasumarthiFacetDependence2023.xlsx
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2246851745043986</v>
+        <v>0.2235437229234776</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1095778606829929</v>
+        <v>0.1080319535341629</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1277538475919344</v>
+        <v>0.1277214236948566</v>
       </c>
       <c r="K3" s="4">
         <v>77.1237244897959</v>
@@ -902,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1889538812737588</v>
+        <v>0.1885712282620324</v>
       </c>
       <c r="I4" s="4">
-        <v>0.09345439539898084</v>
+        <v>0.09183420608496155</v>
       </c>
       <c r="J4" s="4">
-        <v>0.09912643080956657</v>
+        <v>0.09981907127305591</v>
       </c>
       <c r="K4" s="4">
         <v>82.85684940642921</v>
@@ -1461,16 +1461,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8485257318287041</v>
+        <v>-0.8301792304773699</v>
       </c>
       <c r="O3" s="5">
         <v>45</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1323562327661138</v>
+        <v>0.1303030681243399</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1323562327661138</v>
+        <v>0.1303030681243399</v>
       </c>
       <c r="R3" s="5">
         <v>45</v>
@@ -1520,16 +1520,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4577236848349871</v>
+        <v>-0.4790320818538021</v>
       </c>
       <c r="O4" s="5">
         <v>44</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09383914091960066</v>
+        <v>0.09306973771841016</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09383914091960066</v>
+        <v>0.09306973771841016</v>
       </c>
       <c r="R4" s="5">
         <v>44</v>
@@ -1579,16 +1579,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>-2.008261740876575</v>
+        <v>-1.990501359665359</v>
       </c>
       <c r="O5" s="5">
         <v>30</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1185777885646744</v>
+        <v>0.1189930275675793</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09645181705706314</v>
+        <v>0.09558102068549487</v>
       </c>
       <c r="R5" s="5">
         <v>30</v>
@@ -1638,16 +1638,16 @@
         <v>19</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.19932357874859</v>
+        <v>-2.167938816888636</v>
       </c>
       <c r="O6" s="5">
         <v>22</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1465948554880125</v>
+        <v>0.1522199954414453</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1230605664432832</v>
+        <v>0.1212203371102408</v>
       </c>
       <c r="R6" s="5">
         <v>22</v>
@@ -1697,16 +1697,16 @@
         <v>4</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.855875738802535</v>
+        <v>-1.816024353342073</v>
       </c>
       <c r="O7" s="5">
         <v>21</v>
       </c>
       <c r="P7" s="4">
-        <v>0.648937938302367</v>
+        <v>0.6630031331707655</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1132491137825804</v>
+        <v>0.1113514287606536</v>
       </c>
       <c r="R7" s="5">
         <v>21</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.356491776914599</v>
+        <v>-1.353555978057557</v>
       </c>
       <c r="O8" s="5">
         <v>31</v>
@@ -1765,7 +1765,7 @@
         <v>0.1023773606339091</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.09906360156322373</v>
+        <v>0.09896889837428686</v>
       </c>
       <c r="R8" s="5">
         <v>31</v>
@@ -1815,16 +1815,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.250883509961726</v>
+        <v>-1.279499890508305</v>
       </c>
       <c r="O9" s="5">
         <v>23</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2083668696633512</v>
+        <v>0.1988980127716786</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1222929155329372</v>
+        <v>0.1178190648121096</v>
       </c>
       <c r="R9" s="5">
         <v>23</v>
@@ -1874,16 +1874,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.06385642543871654</v>
+        <v>-0.05674604923115112</v>
       </c>
       <c r="O10" s="5">
         <v>25</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1419019075383428</v>
+        <v>0.1423843468430027</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1022713380757487</v>
+        <v>0.1016933074759436</v>
       </c>
       <c r="R10" s="5">
         <v>25</v>
@@ -1933,16 +1933,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.261090187271394</v>
+        <v>-1.304150598360138</v>
       </c>
       <c r="O11" s="5">
         <v>18</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3313264814326249</v>
+        <v>0.316996230569057</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1619116110815401</v>
+        <v>0.1587542003055407</v>
       </c>
       <c r="R11" s="5">
         <v>18</v>
@@ -1992,16 +1992,16 @@
         <v>20</v>
       </c>
       <c r="N12" s="4">
-        <v>-2.13064501501535</v>
+        <v>-2.092933457286563</v>
       </c>
       <c r="O12" s="5">
         <v>23</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1095194438591842</v>
+        <v>0.1080109815500327</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1009537727649982</v>
+        <v>0.09931413982026836</v>
       </c>
       <c r="R12" s="5">
         <v>23</v>
@@ -2051,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-1.529201592586712</v>
+        <v>-1.516487632910867</v>
       </c>
       <c r="O13" s="5">
         <v>12</v>
       </c>
       <c r="P13" s="4">
-        <v>0.6806483764339645</v>
+        <v>0.6826558437512033</v>
       </c>
       <c r="Q13" s="4">
         <v>0.1308584962292419</v>
@@ -2110,16 +2110,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.709509118863934</v>
+        <v>-1.745326798485621</v>
       </c>
       <c r="O14" s="5">
         <v>12</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4170793937137205</v>
+        <v>0.3997072557511274</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.07678325865890656</v>
+        <v>0.0717081484690425</v>
       </c>
       <c r="R14" s="5">
         <v>12</v>
@@ -2167,13 +2167,13 @@
         <v>12</v>
       </c>
       <c r="N15" s="4">
-        <v>-2.247424341459312</v>
+        <v>-2.257626093476574</v>
       </c>
       <c r="O15" s="5">
         <v>12</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1118748072911633</v>
+        <v>0.1105995882890056</v>
       </c>
       <c r="Q15" s="4">
         <v>0.08947386380532407</v>
@@ -2226,16 +2226,16 @@
         <v>3</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.934894883694402</v>
+        <v>-1.952112115479395</v>
       </c>
       <c r="O16" s="5">
         <v>14</v>
       </c>
       <c r="P16" s="4">
-        <v>0.08913533517535101</v>
+        <v>0.08766729990044647</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.0766823824230173</v>
+        <v>0.07633928975597623</v>
       </c>
       <c r="R16" s="5">
         <v>14</v>
@@ -2408,16 +2408,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2072148357632236</v>
+        <v>-0.174226352224883</v>
       </c>
       <c r="O3" s="5">
         <v>132</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1039704999515591</v>
+        <v>0.1033692179906432</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08207217571359156</v>
+        <v>0.07943515038908433</v>
       </c>
       <c r="R3" s="5">
         <v>132</v>
@@ -2467,16 +2467,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1849463444931472</v>
+        <v>-0.1955450714563796</v>
       </c>
       <c r="O4" s="5">
         <v>119</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1217816021199155</v>
+        <v>0.120711039409304</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1135202785679999</v>
+        <v>0.113000301461715</v>
       </c>
       <c r="R4" s="5">
         <v>119</v>
@@ -2526,16 +2526,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7421998810099455</v>
+        <v>-0.7294841193508574</v>
       </c>
       <c r="O5" s="5">
         <v>107</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09942249576447777</v>
+        <v>0.09961337244009835</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07884929364263252</v>
+        <v>0.07810373031948918</v>
       </c>
       <c r="R5" s="5">
         <v>107</v>
@@ -2585,16 +2585,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5945000713920967</v>
+        <v>-0.5842194823232951</v>
       </c>
       <c r="O6" s="5">
         <v>102</v>
       </c>
       <c r="P6" s="4">
-        <v>0.08917423772709016</v>
+        <v>0.08929000065805053</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.08494130042409426</v>
+        <v>0.0844591324057698</v>
       </c>
       <c r="R6" s="5">
         <v>102</v>
@@ -2644,16 +2644,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7221856090380683</v>
+        <v>-0.7157750387953143</v>
       </c>
       <c r="O7" s="5">
         <v>67</v>
       </c>
       <c r="P7" s="4">
-        <v>0.4980368309279123</v>
+        <v>0.4996886834310936</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1020780914056478</v>
+        <v>0.1018723361699536</v>
       </c>
       <c r="R7" s="5">
         <v>67</v>
@@ -2703,16 +2703,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2935755266860084</v>
+        <v>-0.2868724813751165</v>
       </c>
       <c r="O8" s="5">
         <v>99</v>
       </c>
       <c r="P8" s="4">
-        <v>0.06595677095983789</v>
+        <v>0.06582317384654449</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.0660149846059047</v>
+        <v>0.06581233049842762</v>
       </c>
       <c r="R8" s="5">
         <v>99</v>
@@ -2762,16 +2762,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.395232682680719</v>
+        <v>-0.381841851299674</v>
       </c>
       <c r="O9" s="5">
         <v>82</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2636176115108348</v>
+        <v>0.2650862987039856</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.09486367283325792</v>
+        <v>0.09386069598745493</v>
       </c>
       <c r="R9" s="5">
         <v>82</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.06577525609057178</v>
+        <v>-0.05935181787985755</v>
       </c>
       <c r="O10" s="5">
         <v>79</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1654987478315165</v>
+        <v>0.166275207395449</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1022389729834264</v>
+        <v>0.102157663638987</v>
       </c>
       <c r="R10" s="5">
         <v>79</v>
@@ -2880,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.4277782645557701</v>
+        <v>-0.3772314668024208</v>
       </c>
       <c r="O11" s="5">
         <v>83</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1142954285798121</v>
+        <v>0.1057432796212217</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1125999318213191</v>
+        <v>0.1026237118576218</v>
       </c>
       <c r="R11" s="5">
         <v>83</v>
@@ -2939,16 +2939,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.7136178329554733</v>
+        <v>-0.7299479030300127</v>
       </c>
       <c r="O12" s="5">
         <v>63</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1507640077299417</v>
+        <v>0.1481512861958481</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1238664527073877</v>
+        <v>0.1232133523933578</v>
       </c>
       <c r="R12" s="5">
         <v>63</v>
@@ -2998,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.4384732707200284</v>
+        <v>-0.4085213985909659</v>
       </c>
       <c r="O13" s="5">
         <v>58</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4426566280913722</v>
+        <v>0.4435753485154173</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1052092762803198</v>
+        <v>0.1016862125035205</v>
       </c>
       <c r="R13" s="5">
         <v>58</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.5305350749042023</v>
+        <v>-0.5081598262529194</v>
       </c>
       <c r="O14" s="5">
         <v>50</v>
       </c>
       <c r="P14" s="4">
-        <v>0.2536585029425361</v>
+        <v>0.2567258106873504</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.08840984691756087</v>
+        <v>0.0870886334644079</v>
       </c>
       <c r="R14" s="5">
         <v>50</v>
@@ -3116,13 +3116,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.5907477696629828</v>
+        <v>-0.59241667157821</v>
       </c>
       <c r="O15" s="5">
         <v>30</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3711836407698618</v>
+        <v>0.3708498603868164</v>
       </c>
       <c r="Q15" s="4">
         <v>0.06710083540820974</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.6772366297027517</v>
+        <v>-0.6778802694828556</v>
       </c>
       <c r="O16" s="5">
         <v>41</v>
       </c>
       <c r="P16" s="4">
-        <v>0.09572973418551789</v>
+        <v>0.09568482908458041</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.08689044742835923</v>
+        <v>0.0868747488971372</v>
       </c>
       <c r="R16" s="5">
         <v>41</v>
